--- a/data/trans_orig/IP11-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP11-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>13243</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8313</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20021</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13,08%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>12888</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7912</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>19143</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>7944</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18852</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>9,29%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>13,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>13243</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>8127</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>19910</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>8,65%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18814</t>
+          <t>18879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34523</t>
+          <t>35122</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,04%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>139834</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>133056</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>144764</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>91,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>86,92%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>125838</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>119583</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>130814</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>119874</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>130782</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>90,71%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>86,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>139834</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>133167</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>144950</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>91,35%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257280</t>
+          <t>256681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>272989</t>
+          <t>272924</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,53%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13703</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8633</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>20194</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,46%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,52%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>7045</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3837</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12224</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3646</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>11417</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>3,61%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>13703</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>8414</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>19649</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14459</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27734</t>
+          <t>28390</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>198439</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>191948</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>203509</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,54%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>300</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>188118</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>182939</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>191326</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>183746</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>191517</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>96,39%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>198439</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>192493</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>203728</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>379571</t>
+          <t>378915</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>392846</t>
+          <t>392883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8895</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4839</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14147</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6332</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2842</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10961</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3181</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11378</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8895</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4818</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14314</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,94%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>9795</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22481</t>
+          <t>22163</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>140762</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>135510</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>144818</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,77%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>131485</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>126856</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>134975</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>126439</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>134636</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,94%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>140762</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>135343</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>144839</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,06%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>264993</t>
+          <t>265311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>277304</t>
+          <t>277679</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10685</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6566</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16831</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>9039</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5085</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14413</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4704</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14983</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,32%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10685</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6522</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16664</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13862</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>27507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>197139</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>190993</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>201258</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,86%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>262</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>200276</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>194902</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>204230</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>194332</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>204611</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,68%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>197139</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>191160</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>201302</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,86%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>389811</t>
+          <t>389632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>403277</t>
+          <t>403508</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,73%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>46525</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>36682</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>58494</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>35304</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>26187</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>45694</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>26221</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>45310</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>5,18%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>3,85%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,71%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>46525</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>36605</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>58829</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>5,07%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69001</t>
+          <t>69862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>96090</t>
+          <t>96898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -2208,74 +2208,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>676175</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>664206</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>686018</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>93,56%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>91,91%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,92%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>965</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>645717</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>635327</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>654834</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>635711</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>654800</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>94,82%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93,29%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>93,35%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>96,15%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1016</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>676175</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>663871</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>686095</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>93,56%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>91,86%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1981</t>
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1307631</t>
+          <t>1306823</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1334720</t>
+          <t>1333859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>16370</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10217</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>23992</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>10,58%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,61%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>15,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>9073</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4865</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>14710</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4947</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>14534</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>6,51%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>10,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>16370</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10761</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24030</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18231</t>
+          <t>18093</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33311</t>
+          <t>34592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,76%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>138314</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>130692</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>144467</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>89,42%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>84,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,39%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>130284</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>124647</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>134492</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>124823</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>134410</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>93,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>89,44%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>138314</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>130654</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>143923</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>89,42%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>260730</t>
+          <t>259449</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>275810</t>
+          <t>275948</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>19495</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>13582</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27032</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>8,71%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,07%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>21431</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15017</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>29556</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>15136</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29125</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>10,39%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,28%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>19495</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>13082</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>27515</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>8,71%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31762</t>
+          <t>31635</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51272</t>
+          <t>51577</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>204340</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>196803</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>210253</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>91,29%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>184927</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>176802</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>191341</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>177233</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>191222</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>89,61%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>85,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>296</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>204340</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>196320</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>210753</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>91,29%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>378921</t>
+          <t>378616</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>398431</t>
+          <t>398558</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,65%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223835</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18141</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12525</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25801</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,54%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8499</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4851</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>14092</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4679</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>14225</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,48%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>18141</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12543</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>25888</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,93%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19735</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>36110</t>
+          <t>34642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>10,79%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>147844</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>140184</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>153460</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,46%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>146466</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>140873</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>150114</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>140740</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>150286</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,52%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,91%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>147844</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>140097</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>153442</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>89,07%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>284840</t>
+          <t>286308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>301215</t>
+          <t>301127</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165985</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>154965</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>154965</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>154965</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165985</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>19371</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>13136</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>27344</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,36%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>13,24%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>12709</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7881</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19553</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7475</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19410</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,04%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,75%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>19371</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>12218</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>27291</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>23680</t>
+          <t>23817</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>42258</t>
+          <t>41870</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>187194</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>179221</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>193429</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,64%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>197591</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>190747</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>202419</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>190890</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>202825</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,96%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>90,7%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>96,25%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>187194</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>179274</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>194347</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,62%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>374607</t>
+          <t>374995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>393185</t>
+          <t>393048</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206565</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206565</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206565</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206565</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206565</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206565</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>73377</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>61136</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>87643</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>11,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>51712</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>40579</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>65077</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>41292</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>63464</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>7,27%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>9,15%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>73377</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>60540</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>87567</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>9,77%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108681</t>
+          <t>108382</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142229</t>
+          <t>143766</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>966</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>677692</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>663426</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>689933</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>90,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>88,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>91,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>949</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>659268</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>645903</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>670401</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>647516</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>669688</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>92,73%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>90,85%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>966</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>677692</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>663502</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>690529</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>90,23%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1319820</t>
+          <t>1318283</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1353368</t>
+          <t>1353667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1071</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>751069</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>751069</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>751069</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>710980</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>710980</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>710980</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1071</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>751069</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>751069</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>751069</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9981</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5727</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>16317</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,77%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,89%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>6996</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3320</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11889</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>3417</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12773</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>5,23%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,89%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>9981</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>5296</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>16188</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>6,77%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>11039</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>24686</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>137416</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>131080</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>141670</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,23%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>88,93%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>96,11%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>126711</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>121818</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>130387</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>120934</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>130290</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>94,77%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,11%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>97,52%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>137416</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>131209</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>142101</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>93,23%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257264</t>
+          <t>256418</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>270364</t>
+          <t>270065</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147397</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147397</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147397</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147397</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147397</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147397</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11082</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6789</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17443</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,8%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>8955</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4982</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13729</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4964</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14198</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,33%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11082</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6459</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16580</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,95%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13993</t>
+          <t>14283</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27825</t>
+          <t>27414</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>212615</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>206254</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>216908</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,2%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>197675</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>192901</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>201648</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>192432</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>201666</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,67%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>212615</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>207117</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>217238</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,05%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>402502</t>
+          <t>402913</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>416334</t>
+          <t>416044</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223697</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223697</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223697</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206630</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206630</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206630</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>331</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223697</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223697</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223697</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7892</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12971</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,78%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4465</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8711</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2078</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8324</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,86%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7892</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4474</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13097</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,73%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>18480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158781</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>153702</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>162290</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,27%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,22%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,37%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>151532</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>147286</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>153983</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>147673</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>153919</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,14%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>158781</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>153576</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>162199</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,27%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>303339</t>
+          <t>304190</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>314550</t>
+          <t>314708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11769</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6877</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18505</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>2954</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7461</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7188</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,44%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,36%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>11769</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7116</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18769</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9366</t>
+          <t>9118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>23363</t>
+          <t>22745</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>193967</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>187231</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>198859</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,28%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,01%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>202774</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>198267</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>204990</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>198540</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>204989</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,56%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>96,51%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,64%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>193967</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>186967</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>198620</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,28%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>549</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>388101</t>
+          <t>388719</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>402098</t>
+          <t>402346</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205728</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205728</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205728</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>40724</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30622</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>52365</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,04%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>23369</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17224</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>31776</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>16176</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>31456</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,53%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>40724</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>31377</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>52052</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,48%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52697</t>
+          <t>52656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76910</t>
+          <t>78791</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>702779</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>691138</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>712881</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>92,96%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1022</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>678692</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>670285</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>684837</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>670605</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>685885</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,67%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,47%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,55%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>702779</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>691451</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>712126</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>94,52%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1368654</t>
+          <t>1366773</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1392867</t>
+          <t>1392908</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,36%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>743503</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>743503</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>743503</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>702061</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>702061</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>702061</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>743503</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>538</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5572</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3497</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1348</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>7465</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,37%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>3644</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5807</t>
+          <t>9165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5805</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2720</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>123693</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>120334</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>125368</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,57%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>113783</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>109815</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>115932</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,63%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>138104</t>
+          <t>117427</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134605</t>
+          <t>111906</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139819</t>
+          <t>119716</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>251888</t>
+          <t>241120</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247081</t>
+          <t>235844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>254973</t>
+          <t>244275</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1602</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>12216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>9341</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>10431</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5656</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>230412</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>223991</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>233678</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>185980</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>180810</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>188910</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,91%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>248056</t>
+          <t>179798</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>242016</t>
+          <t>175072</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>251531</t>
+          <t>182631</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>434037</t>
+          <t>410210</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>426747</t>
+          <t>402910</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>439102</t>
+          <t>414964</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>236207</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>236207</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>236207</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>253955</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>253955</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>253955</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>444468</t>
+          <t>420620</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>444468</t>
+          <t>420620</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>444468</t>
+          <t>420620</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7498</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3380</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13619</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6546</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2559</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12198</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>6352</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15781</t>
+          <t>11631</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14835</t>
+          <t>13850</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9039</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24661</t>
+          <t>21691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>160843</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>154722</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164961</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,55%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>182623</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>176971</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>186610</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,55%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,65%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>176997</t>
+          <t>149493</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>169505</t>
+          <t>144214</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>181339</t>
+          <t>152931</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>359620</t>
+          <t>310336</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>349794</t>
+          <t>302495</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>365416</t>
+          <t>315997</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>189169</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>189169</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>189169</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155845</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155845</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374455</t>
+          <t>324186</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374455</t>
+          <t>324186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374455</t>
+          <t>324186</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6746</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3399</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12153</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,98%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2577</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,74%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7538</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13259</t>
+          <t>6588</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>10115</t>
+          <t>9318</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5848</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16652</t>
+          <t>15159</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>162630</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>157223</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>165977</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,82%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,99%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>165385</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>161688</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167292</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,26%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>173700</t>
+          <t>164573</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>167979</t>
+          <t>160557</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>177742</t>
+          <t>166508</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>339086</t>
+          <t>327203</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>332549</t>
+          <t>321362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>343353</t>
+          <t>331568</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14992</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>32709</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17151</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10652</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>25105</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16368</t>
+          <t>11864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35058</t>
+          <t>25644</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41185</t>
+          <t>39435</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>29937</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>52614</t>
+          <t>50648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>677579</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>667121</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>684838</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,82%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,33%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97,86%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>647773</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>639819</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>654272</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,22%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>736858</t>
+          <t>611290</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>725834</t>
+          <t>602830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>744524</t>
+          <t>616610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1384631</t>
+          <t>1288870</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1373202</t>
+          <t>1277657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1395879</t>
+          <t>1298582</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,76%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699830</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699830</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699830</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760892</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425816</t>
+          <t>1328305</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425816</t>
+          <t>1328305</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425816</t>
+          <t>1328305</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
